--- a/副本SNE25051水城钢铁轧钢加热炉超低排放改造-三棒加热炉调试记录2026.8.28.xlsx
+++ b/副本SNE25051水城钢铁轧钢加热炉超低排放改造-三棒加热炉调试记录2026.8.28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wk-sh\Desktop\git版本管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CA2458-C94F-4EDD-A70C-D6344C0E81B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC17D420-0DC5-4F6D-BCAD-EFCC2D7A2DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{45E888AC-7810-4C09-8C05-2AF88F91C25A}"/>
   </bookViews>
@@ -34,11 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>8月25日水钢三棒加热炉调试记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>煤气总量</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,10 +60,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>经过2次转手动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>测试时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,9 +72,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>投入自动</t>
-  </si>
-  <si>
     <t>调试情况：</t>
   </si>
   <si>
@@ -94,14 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>直径12 热钢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>切换手动，煤气瞬时值11237</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 切换原因：热值波动 8000-6000 降得太多（怕红钢烧出问题）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -135,6 +116,22 @@
   </si>
   <si>
     <t>本次主要测试了所有均热段烧嘴和下加烧嘴，上均左因煤气总管流量保持在2000左右，判断不可信，希望再将流量计拆下将残留煤焦油进行彻底清理，本次测试控制平稳，因煤气热值低于8000转为手动，所有烧嘴已经测试完毕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8:00-10:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未生产，无法投用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9月1日水钢三棒加热炉投用记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据现场要求，对每个PLC梯形图再进行一次保存动作。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -551,7 +548,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -565,91 +562,64 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2915517</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2995086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <v>8274</v>
-      </c>
-      <c r="C5" s="1">
-        <v>7173.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>15</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <v>10744</v>
-      </c>
-      <c r="C7" s="1">
-        <v>10690</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.40138888888888891</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.70416666666666672</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1</v>
       </c>
-      <c r="B12" s="2">
-        <v>0.40138888888888891</v>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -657,10 +627,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="2">
-        <v>0.46527777777777779</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -671,10 +641,10 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -685,7 +655,7 @@
         <v>0.58680555555555558</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="56" x14ac:dyDescent="0.3">
@@ -696,10 +666,10 @@
         <v>0.63402777777777775</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" x14ac:dyDescent="0.3">
@@ -710,7 +680,7 @@
         <v>0.64027777777777772</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -721,7 +691,7 @@
         <v>0.68125000000000002</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.3">
@@ -732,15 +702,15 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>

--- a/副本SNE25051水城钢铁轧钢加热炉超低排放改造-三棒加热炉调试记录2026.8.28.xlsx
+++ b/副本SNE25051水城钢铁轧钢加热炉超低排放改造-三棒加热炉调试记录2026.8.28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wk-sh\Desktop\git版本管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC17D420-0DC5-4F6D-BCAD-EFCC2D7A2DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E85AB27-8AA7-4F33-8D3D-22984742DB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{45E888AC-7810-4C09-8C05-2AF88F91C25A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>煤气总量</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,14 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>热值7839.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>师傅说等等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>切换为手动，热值为7487，煤气瞬时值11483</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -132,6 +124,10 @@
   </si>
   <si>
     <t>根据现场要求，对每个PLC梯形图再进行一次保存动作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>热值8056.9，煤气3629152.00，瞬时煤气13186.87，调至自动</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -548,7 +544,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -616,10 +612,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -630,21 +626,18 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>3</v>
       </c>
       <c r="B14" s="2">
-        <v>0.57291666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -666,7 +659,7 @@
         <v>0.63402777777777775</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -680,7 +673,7 @@
         <v>0.64027777777777772</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -691,7 +684,7 @@
         <v>0.68125000000000002</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.3">
@@ -702,7 +695,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -710,7 +703,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
